--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RskSpecificAssetType001.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RskSpecificAssetType001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\tams_v1\tams-invest-parent\tams-invest-risk\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\tams\tams-invest-parent\tams-invest-risk\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,19 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>资产一级分类</t>
-  </si>
-  <si>
-    <t>资产二级分类</t>
-  </si>
-  <si>
-    <t>资产三级分类</t>
-  </si>
-  <si>
-    <t>业务分类</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>资产代码</t>
   </si>
@@ -416,18 +404,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="4" max="4" width="20.25" customWidth="1"/>
-    <col min="7" max="7" width="31.125" customWidth="1"/>
-    <col min="8" max="8" width="33.75" customWidth="1"/>
-    <col min="9" max="9" width="44.5" customWidth="1"/>
-    <col min="10" max="10" width="18.75" customWidth="1"/>
+    <col min="3" max="3" width="31.08984375" customWidth="1"/>
+    <col min="4" max="4" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.453125" customWidth="1"/>
+    <col min="6" max="6" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -440,23 +426,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -469,7 +443,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -480,7 +454,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RskSpecificAssetType001.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RskSpecificAssetType001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\tams\tams-invest-parent\tams-invest-risk\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\tams-3.0\tams\tams-invest-parent\tams-invest-risk\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,9 +29,6 @@
     <t>资产名称</t>
   </si>
   <si>
-    <t>是否不良资产/收受益权</t>
-  </si>
-  <si>
     <t>是否国务院银行业监督管理机构另有规定</t>
   </si>
   <si>
@@ -39,7 +36,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>是否信贷资产</t>
+    <t>是否不良资产及其受（收）益权</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否信贷资产及其受（收）益权</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -405,15 +406,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="3" max="3" width="31.08984375" customWidth="1"/>
-    <col min="4" max="4" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.453125" customWidth="1"/>
-    <col min="6" max="6" width="18.7265625" customWidth="1"/>
+    <col min="3" max="3" width="31.125" customWidth="1"/>
+    <col min="4" max="4" width="39.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.5" customWidth="1"/>
+    <col min="6" max="6" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -421,16 +422,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -443,7 +444,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -454,7 +455,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
